--- a/exercises/ex0/images/Basis for Screenshot-02.xlsx
+++ b/exercises/ex0/images/Basis for Screenshot-02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D038335\github\teched2026-BT164\exercises\ex0\images\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E80B250D-DA5C-4104-8435-2B1F9DF1415C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D306BDBF-56E5-4FF0-80C8-5BA43CDB03D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8535" yWindow="2145" windowWidth="45855" windowHeight="20370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Hands-On Exercise Overview</t>
   </si>
@@ -119,10 +119,7 @@
     <t>Exercise 9</t>
   </si>
   <si>
-    <t>Exercise 10</t>
-  </si>
-  <si>
-    <t>Skipped in this Hands-On</t>
+    <t>Exercise A</t>
   </si>
 </sst>
 </file>
@@ -153,7 +150,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -205,12 +202,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="-0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -227,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -253,24 +244,17 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -558,654 +542,332 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C3:M54"/>
+  <dimension ref="C3:K25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="0.7109375" style="11" customWidth="1"/>
+    <col min="3" max="3" width="0.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="40.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="0.7109375" style="11" customWidth="1"/>
+    <col min="5" max="5" width="0.7109375" style="1" customWidth="1"/>
     <col min="6" max="6" width="40.140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="2.7109375" style="11" customWidth="1"/>
+    <col min="7" max="7" width="2.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="40.140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="2.7109375" style="11" customWidth="1"/>
+    <col min="9" max="9" width="2.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="40.140625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="0.7109375" style="11" customWidth="1"/>
+    <col min="11" max="11" width="0.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:13" s="9" customFormat="1" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-    </row>
-    <row r="4" spans="3:13" ht="21" x14ac:dyDescent="0.25">
-      <c r="C4" s="15"/>
-      <c r="D4" s="12" t="s">
+    <row r="3" spans="3:11" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+    </row>
+    <row r="4" spans="3:11" ht="21" x14ac:dyDescent="0.25">
+      <c r="C4" s="12"/>
+      <c r="D4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="15"/>
-    </row>
-    <row r="5" spans="3:13" s="9" customFormat="1" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5"/>
-      <c r="M5"/>
-    </row>
-    <row r="6" spans="3:13" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C6" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="12"/>
+    </row>
+    <row r="5" spans="3:11" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+    </row>
+    <row r="6" spans="3:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C6" s="10"/>
       <c r="D6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="13"/>
+      <c r="E6" s="10"/>
       <c r="F6" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G6" s="10"/>
+      <c r="G6" s="9"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="10"/>
+      <c r="I6" s="9"/>
       <c r="J6" s="2"/>
-      <c r="K6" s="13"/>
-    </row>
-    <row r="7" spans="3:13" s="9" customFormat="1" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="13"/>
-      <c r="L7"/>
-      <c r="M7"/>
-    </row>
-    <row r="8" spans="3:13" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C8" s="13"/>
+      <c r="K6" s="10"/>
+    </row>
+    <row r="7" spans="3:11" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="10"/>
+    </row>
+    <row r="8" spans="3:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C8" s="10"/>
       <c r="D8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="13"/>
+        <v>27</v>
+      </c>
+      <c r="E8" s="10"/>
       <c r="F8" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G8" s="10"/>
+      <c r="G8" s="9"/>
       <c r="H8" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I8" s="10"/>
+      <c r="I8" s="9"/>
       <c r="J8" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="K8" s="13"/>
-    </row>
-    <row r="9" spans="3:13" s="9" customFormat="1" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="13"/>
-      <c r="L9"/>
-      <c r="M9"/>
-    </row>
-    <row r="10" spans="3:13" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C10" s="13"/>
+      <c r="K8" s="10"/>
+    </row>
+    <row r="9" spans="3:11" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="10"/>
+    </row>
+    <row r="10" spans="3:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C10" s="10"/>
       <c r="D10" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="13"/>
+        <v>19</v>
+      </c>
+      <c r="E10" s="10"/>
       <c r="F10" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G10" s="10"/>
+      <c r="G10" s="9"/>
       <c r="H10" s="2"/>
-      <c r="I10" s="10"/>
+      <c r="I10" s="9"/>
       <c r="J10" s="2"/>
-      <c r="K10" s="13"/>
-    </row>
-    <row r="11" spans="3:13" s="9" customFormat="1" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="13"/>
-      <c r="L11"/>
-      <c r="M11"/>
-    </row>
-    <row r="12" spans="3:13" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C12" s="13"/>
+      <c r="K10" s="10"/>
+    </row>
+    <row r="11" spans="3:11" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="10"/>
+    </row>
+    <row r="12" spans="3:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C12" s="10"/>
       <c r="D12" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="13"/>
+        <v>20</v>
+      </c>
+      <c r="E12" s="10"/>
       <c r="F12" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="10"/>
+      <c r="G12" s="9"/>
       <c r="H12" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I12" s="10"/>
+      <c r="I12" s="9"/>
       <c r="J12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="13"/>
-    </row>
-    <row r="13" spans="3:13" s="9" customFormat="1" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="13"/>
-    </row>
-    <row r="14" spans="3:13" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C14" s="13"/>
+      <c r="K12" s="10"/>
+    </row>
+    <row r="13" spans="3:11" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="10"/>
+    </row>
+    <row r="14" spans="3:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="10"/>
       <c r="D14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="13"/>
+        <v>21</v>
+      </c>
+      <c r="E14" s="10"/>
       <c r="F14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="G14" s="10"/>
+      <c r="G14" s="9"/>
       <c r="H14" s="2"/>
-      <c r="I14" s="10"/>
+      <c r="I14" s="9"/>
       <c r="J14" s="2"/>
-      <c r="K14" s="13"/>
-    </row>
-    <row r="15" spans="3:13" s="9" customFormat="1" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="13"/>
-    </row>
-    <row r="16" spans="3:13" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C16" s="13"/>
+      <c r="K14" s="10"/>
+    </row>
+    <row r="15" spans="3:11" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="10"/>
+    </row>
+    <row r="16" spans="3:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="10"/>
       <c r="D16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" s="13"/>
+        <v>22</v>
+      </c>
+      <c r="E16" s="10"/>
       <c r="F16" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="10"/>
+      <c r="G16" s="9"/>
       <c r="H16" s="2"/>
-      <c r="I16" s="10"/>
+      <c r="I16" s="9"/>
       <c r="J16" s="2"/>
-      <c r="K16" s="13"/>
-    </row>
-    <row r="17" spans="3:11" s="9" customFormat="1" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="13"/>
+      <c r="K16" s="10"/>
+    </row>
+    <row r="17" spans="3:11" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="10"/>
     </row>
     <row r="18" spans="3:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C18" s="13"/>
+      <c r="C18" s="10"/>
       <c r="D18" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="13"/>
+        <v>23</v>
+      </c>
+      <c r="E18" s="10"/>
       <c r="F18" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G18" s="10"/>
+      <c r="G18" s="9"/>
       <c r="H18" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I18" s="10"/>
+      <c r="I18" s="9"/>
       <c r="J18" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="K18" s="13"/>
-    </row>
-    <row r="19" spans="3:11" s="9" customFormat="1" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="14"/>
-      <c r="K19" s="13"/>
+      <c r="K18" s="10"/>
+    </row>
+    <row r="19" spans="3:11" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="10"/>
     </row>
     <row r="20" spans="3:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C20" s="13"/>
+      <c r="C20" s="10"/>
       <c r="D20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="13"/>
+        <v>24</v>
+      </c>
+      <c r="E20" s="10"/>
       <c r="F20" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G20" s="10"/>
+      <c r="G20" s="9"/>
       <c r="H20" s="2"/>
-      <c r="I20" s="10"/>
+      <c r="I20" s="9"/>
       <c r="J20" s="2"/>
-      <c r="K20" s="13"/>
-    </row>
-    <row r="21" spans="3:11" s="9" customFormat="1" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="14"/>
-      <c r="K21" s="13"/>
+      <c r="K20" s="10"/>
+    </row>
+    <row r="21" spans="3:11" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="10"/>
     </row>
     <row r="22" spans="3:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C22" s="13"/>
+      <c r="C22" s="10"/>
       <c r="D22" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22" s="13"/>
+        <v>25</v>
+      </c>
+      <c r="E22" s="10"/>
       <c r="F22" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G22" s="10"/>
+      <c r="G22" s="9"/>
       <c r="H22" s="2"/>
-      <c r="I22" s="10"/>
+      <c r="I22" s="9"/>
       <c r="J22" s="2"/>
-      <c r="K22" s="13"/>
-    </row>
-    <row r="23" spans="3:11" s="9" customFormat="1" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="14"/>
-      <c r="K23" s="13"/>
+      <c r="K22" s="10"/>
+    </row>
+    <row r="23" spans="3:11" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="10"/>
     </row>
     <row r="24" spans="3:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C24" s="13"/>
+      <c r="C24" s="10"/>
       <c r="D24" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E24" s="13"/>
+        <v>26</v>
+      </c>
+      <c r="E24" s="10"/>
       <c r="F24" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G24" s="10"/>
+      <c r="G24" s="9"/>
       <c r="H24" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I24" s="10"/>
+      <c r="I24" s="9"/>
       <c r="J24" s="2"/>
-      <c r="K24" s="13"/>
-    </row>
-    <row r="25" spans="3:11" s="9" customFormat="1" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="13"/>
-    </row>
-    <row r="32" spans="3:11" s="9" customFormat="1" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="13"/>
-      <c r="K32" s="13"/>
-    </row>
-    <row r="33" spans="3:13" ht="21" x14ac:dyDescent="0.25">
-      <c r="C33" s="15"/>
-      <c r="D33" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="15"/>
-    </row>
-    <row r="34" spans="3:13" s="9" customFormat="1" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="13"/>
-      <c r="J34" s="13"/>
-      <c r="K34" s="13"/>
-      <c r="L34"/>
-      <c r="M34"/>
-    </row>
-    <row r="35" spans="3:13" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C35" s="13"/>
-      <c r="D35" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E35" s="13"/>
-      <c r="F35" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="G35" s="10"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="10"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="13"/>
-    </row>
-    <row r="36" spans="3:13" s="9" customFormat="1" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="13"/>
-      <c r="J36" s="14"/>
-      <c r="K36" s="13"/>
-      <c r="L36"/>
-      <c r="M36"/>
-    </row>
-    <row r="37" spans="3:13" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="13"/>
-      <c r="D37" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E37" s="13"/>
-      <c r="F37" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="13"/>
-    </row>
-    <row r="38" spans="3:13" s="9" customFormat="1" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="14"/>
-      <c r="K38" s="13"/>
-      <c r="L38"/>
-      <c r="M38"/>
-    </row>
-    <row r="39" spans="3:13" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="13"/>
-      <c r="D39" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E39" s="13"/>
-      <c r="F39" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="G39" s="10"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="10"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="13"/>
-    </row>
-    <row r="40" spans="3:13" s="9" customFormat="1" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="13"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="13"/>
-      <c r="J40" s="14"/>
-      <c r="K40" s="13"/>
-      <c r="L40"/>
-      <c r="M40"/>
-    </row>
-    <row r="41" spans="3:13" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="13"/>
-      <c r="D41" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E41" s="13"/>
-      <c r="F41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G41" s="10"/>
-      <c r="H41" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I41" s="10"/>
-      <c r="J41" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="K41" s="13"/>
-    </row>
-    <row r="42" spans="3:13" s="9" customFormat="1" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="13"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="13"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="13"/>
-      <c r="J42" s="14"/>
-      <c r="K42" s="13"/>
-    </row>
-    <row r="43" spans="3:13" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="13"/>
-      <c r="D43" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E43" s="13"/>
-      <c r="F43" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G43" s="10"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="2"/>
-      <c r="K43" s="13"/>
-    </row>
-    <row r="44" spans="3:13" s="9" customFormat="1" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C44" s="13"/>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="13"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="13"/>
-      <c r="J44" s="14"/>
-      <c r="K44" s="13"/>
-    </row>
-    <row r="45" spans="3:13" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C45" s="13"/>
-      <c r="D45" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E45" s="13"/>
-      <c r="F45" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G45" s="10"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="10"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="13"/>
-    </row>
-    <row r="46" spans="3:13" s="9" customFormat="1" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C46" s="13"/>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="13"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="13"/>
-      <c r="J46" s="14"/>
-      <c r="K46" s="13"/>
-    </row>
-    <row r="47" spans="3:13" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C47" s="13"/>
-      <c r="D47" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E47" s="13"/>
-      <c r="F47" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G47" s="10"/>
-      <c r="H47" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I47" s="10"/>
-      <c r="J47" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="K47" s="13"/>
-    </row>
-    <row r="48" spans="3:13" s="9" customFormat="1" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C48" s="13"/>
-      <c r="D48" s="13"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="13"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="13"/>
-      <c r="J48" s="14"/>
-      <c r="K48" s="13"/>
-    </row>
-    <row r="49" spans="3:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C49" s="13"/>
-      <c r="D49" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E49" s="13"/>
-      <c r="F49" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G49" s="10"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="10"/>
-      <c r="J49" s="2"/>
-      <c r="K49" s="13"/>
-    </row>
-    <row r="50" spans="3:11" s="9" customFormat="1" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C50" s="13"/>
-      <c r="D50" s="13"/>
-      <c r="E50" s="13"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="13"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="13"/>
-      <c r="J50" s="14"/>
-      <c r="K50" s="13"/>
-    </row>
-    <row r="51" spans="3:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C51" s="13"/>
-      <c r="D51" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E51" s="13"/>
-      <c r="F51" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G51" s="10"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="2"/>
-      <c r="K51" s="13"/>
-    </row>
-    <row r="52" spans="3:11" s="9" customFormat="1" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C52" s="13"/>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="13"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="13"/>
-      <c r="J52" s="14"/>
-      <c r="K52" s="13"/>
-    </row>
-    <row r="53" spans="3:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C53" s="13"/>
-      <c r="D53" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E53" s="13"/>
-      <c r="F53" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G53" s="10"/>
-      <c r="H53" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I53" s="10"/>
-      <c r="J53" s="2"/>
-      <c r="K53" s="13"/>
-    </row>
-    <row r="54" spans="3:11" s="9" customFormat="1" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C54" s="13"/>
-      <c r="D54" s="13"/>
-      <c r="E54" s="13"/>
-      <c r="F54" s="13"/>
-      <c r="G54" s="13"/>
-      <c r="H54" s="13"/>
-      <c r="I54" s="13"/>
-      <c r="J54" s="13"/>
-      <c r="K54" s="13"/>
+      <c r="K24" s="10"/>
+    </row>
+    <row r="25" spans="3:11" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="D4:J4"/>
-    <mergeCell ref="D33:J33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/exercises/ex0/images/Basis for Screenshot-02.xlsx
+++ b/exercises/ex0/images/Basis for Screenshot-02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D038335\github\teched2026-BT164\exercises\ex0\images\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D306BDBF-56E5-4FF0-80C8-5BA43CDB03D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67639EE1-2AE9-493B-AB47-7B48FEE30722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9825" yWindow="915" windowWidth="37155" windowHeight="20325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
   <si>
     <t>Hands-On Exercise Overview</t>
   </si>
@@ -120,13 +120,16 @@
   </si>
   <si>
     <t>Exercise A</t>
+  </si>
+  <si>
+    <t>→</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -148,6 +151,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="10">
@@ -218,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -256,6 +266,9 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -567,7 +580,7 @@
       <c r="J3" s="10"/>
       <c r="K3" s="10"/>
     </row>
-    <row r="4" spans="3:11" ht="21" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C4" s="12"/>
       <c r="D4" s="13" t="s">
         <v>0</v>
@@ -617,7 +630,7 @@
       <c r="J7" s="11"/>
       <c r="K7" s="10"/>
     </row>
-    <row r="8" spans="3:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C8" s="10"/>
       <c r="D8" s="3" t="s">
         <v>27</v>
@@ -626,17 +639,21 @@
       <c r="F8" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G8" s="9"/>
+      <c r="G8" s="14" t="s">
+        <v>28</v>
+      </c>
       <c r="H8" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I8" s="9"/>
+      <c r="I8" s="14" t="s">
+        <v>28</v>
+      </c>
       <c r="J8" s="4" t="s">
         <v>4</v>
       </c>
       <c r="K8" s="10"/>
     </row>
-    <row r="9" spans="3:11" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:11" ht="3.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C9" s="10"/>
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
@@ -682,11 +699,15 @@
       <c r="F12" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="9"/>
+      <c r="G12" s="14" t="s">
+        <v>28</v>
+      </c>
       <c r="H12" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I12" s="9"/>
+      <c r="I12" s="14" t="s">
+        <v>28</v>
+      </c>
       <c r="J12" s="5" t="s">
         <v>8</v>
       </c>
@@ -764,11 +785,15 @@
       <c r="F18" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G18" s="9"/>
+      <c r="G18" s="14" t="s">
+        <v>28</v>
+      </c>
       <c r="H18" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I18" s="9"/>
+      <c r="I18" s="14" t="s">
+        <v>28</v>
+      </c>
       <c r="J18" s="5" t="s">
         <v>12</v>
       </c>
@@ -846,7 +871,9 @@
       <c r="F24" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G24" s="9"/>
+      <c r="G24" s="14" t="s">
+        <v>28</v>
+      </c>
       <c r="H24" s="8" t="s">
         <v>17</v>
       </c>

--- a/exercises/ex0/images/Basis for Screenshot-02.xlsx
+++ b/exercises/ex0/images/Basis for Screenshot-02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D038335\github\teched2026-BT164\exercises\ex0\images\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67639EE1-2AE9-493B-AB47-7B48FEE30722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00D2ADCA-D7C2-47A3-803F-A78FDA3E3FF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9825" yWindow="915" windowWidth="37155" windowHeight="20325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20580" yWindow="1065" windowWidth="43695" windowHeight="20580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
   <si>
     <t>Hands-On Exercise Overview</t>
   </si>
@@ -92,37 +92,138 @@
     <t>Review Run &amp; Postprocess Cycles</t>
   </si>
   <si>
-    <t>Exercise 1</t>
-  </si>
-  <si>
-    <t>Exercise 2</t>
-  </si>
-  <si>
-    <t>Exercise 3</t>
-  </si>
-  <si>
-    <t>Exercise 4</t>
-  </si>
-  <si>
-    <t>Exercise 5</t>
-  </si>
-  <si>
-    <t>Exercise 6</t>
-  </si>
-  <si>
-    <t>Exercise 7</t>
-  </si>
-  <si>
-    <t>Exercise 8</t>
-  </si>
-  <si>
-    <t>Exercise 9</t>
-  </si>
-  <si>
     <t>Exercise A</t>
   </si>
   <si>
     <t>→</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Exercise 1
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(~ 5 min)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Exercise 2
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(~ 10 min)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Exercise 3
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(~ 35 min)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Exercise 4
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(~ 10 min)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Exercise 5
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(~ 10 min)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Exercise 6
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(~ 10 min)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Exercise 7
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(~ 10 min)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Exercise 8
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(~ 15 min)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -264,11 +365,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -555,21 +656,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C3:K25"/>
+  <dimension ref="C3:Q23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="0.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="40.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="23.42578125" style="1" customWidth="1"/>
     <col min="5" max="5" width="0.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="40.140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="2.7109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="40.140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="2.7109375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="40.140625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="0.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="22.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="2.85546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="22.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="2.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="22.140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="2.85546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="22.140625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="2.85546875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="22.140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="2.85546875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="22.140625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="0.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:11" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:17" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -579,21 +686,33 @@
       <c r="I3" s="10"/>
       <c r="J3" s="10"/>
       <c r="K3" s="10"/>
-    </row>
-    <row r="4" spans="3:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+    </row>
+    <row r="4" spans="3:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C4" s="12"/>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="12"/>
-    </row>
-    <row r="5" spans="3:11" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="12"/>
+    </row>
+    <row r="5" spans="3:17" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
@@ -603,11 +722,17 @@
       <c r="I5" s="10"/>
       <c r="J5" s="10"/>
       <c r="K5" s="10"/>
-    </row>
-    <row r="6" spans="3:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
+    </row>
+    <row r="6" spans="3:17" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="10"/>
       <c r="D6" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E6" s="10"/>
       <c r="F6" s="4" t="s">
@@ -615,59 +740,83 @@
       </c>
       <c r="G6" s="9"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="9"/>
+      <c r="I6" s="2"/>
       <c r="J6" s="2"/>
-      <c r="K6" s="10"/>
-    </row>
-    <row r="7" spans="3:11" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="10"/>
+    </row>
+    <row r="7" spans="3:17" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
       <c r="H7" s="11"/>
-      <c r="I7" s="10"/>
+      <c r="I7" s="11"/>
       <c r="J7" s="11"/>
-      <c r="K7" s="10"/>
-    </row>
-    <row r="8" spans="3:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="11"/>
+      <c r="Q7" s="10"/>
+    </row>
+    <row r="8" spans="3:17" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C8" s="10"/>
       <c r="D8" s="3" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E8" s="10"/>
       <c r="F8" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G8" s="14" t="s">
-        <v>28</v>
+      <c r="G8" s="13" t="s">
+        <v>19</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I8" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="J8" s="4" t="s">
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="P8" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="K8" s="10"/>
-    </row>
-    <row r="9" spans="3:11" ht="3.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q8" s="10"/>
+    </row>
+    <row r="9" spans="3:17" ht="3.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C9" s="10"/>
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
       <c r="H9" s="11"/>
-      <c r="I9" s="10"/>
+      <c r="I9" s="11"/>
       <c r="J9" s="11"/>
-      <c r="K9" s="10"/>
-    </row>
-    <row r="10" spans="3:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="10"/>
+    </row>
+    <row r="10" spans="3:17" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" s="10"/>
       <c r="D10" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="5" t="s">
@@ -675,59 +824,95 @@
       </c>
       <c r="G10" s="9"/>
       <c r="H10" s="2"/>
-      <c r="I10" s="9"/>
+      <c r="I10" s="2"/>
       <c r="J10" s="2"/>
-      <c r="K10" s="10"/>
-    </row>
-    <row r="11" spans="3:11" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="10"/>
+    </row>
+    <row r="11" spans="3:17" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
       <c r="H11" s="11"/>
-      <c r="I11" s="10"/>
+      <c r="I11" s="11"/>
       <c r="J11" s="11"/>
-      <c r="K11" s="10"/>
-    </row>
-    <row r="12" spans="3:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="10"/>
+    </row>
+    <row r="12" spans="3:17" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="10"/>
       <c r="D12" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="14" t="s">
-        <v>28</v>
+      <c r="G12" s="13" t="s">
+        <v>19</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I12" s="14" t="s">
-        <v>28</v>
+      <c r="I12" s="13" t="s">
+        <v>19</v>
       </c>
       <c r="J12" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K12" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="L12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="10"/>
-    </row>
-    <row r="13" spans="3:11" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M12" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="N12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O12" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="P12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q12" s="10"/>
+    </row>
+    <row r="13" spans="3:17" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
       <c r="F13" s="11"/>
       <c r="G13" s="10"/>
       <c r="H13" s="11"/>
-      <c r="I13" s="10"/>
+      <c r="I13" s="11"/>
       <c r="J13" s="11"/>
-      <c r="K13" s="10"/>
-    </row>
-    <row r="14" spans="3:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="10"/>
+    </row>
+    <row r="14" spans="3:17" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="10"/>
       <c r="D14" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E14" s="10"/>
       <c r="F14" s="6" t="s">
@@ -735,25 +920,37 @@
       </c>
       <c r="G14" s="9"/>
       <c r="H14" s="2"/>
-      <c r="I14" s="9"/>
+      <c r="I14" s="2"/>
       <c r="J14" s="2"/>
-      <c r="K14" s="10"/>
-    </row>
-    <row r="15" spans="3:11" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="10"/>
+    </row>
+    <row r="15" spans="3:17" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C15" s="10"/>
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
       <c r="F15" s="11"/>
       <c r="G15" s="10"/>
       <c r="H15" s="11"/>
-      <c r="I15" s="10"/>
+      <c r="I15" s="11"/>
       <c r="J15" s="11"/>
-      <c r="K15" s="10"/>
-    </row>
-    <row r="16" spans="3:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="10"/>
+    </row>
+    <row r="16" spans="3:17" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="10"/>
       <c r="D16" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E16" s="10"/>
       <c r="F16" s="6" t="s">
@@ -761,142 +958,157 @@
       </c>
       <c r="G16" s="9"/>
       <c r="H16" s="2"/>
-      <c r="I16" s="9"/>
+      <c r="I16" s="2"/>
       <c r="J16" s="2"/>
-      <c r="K16" s="10"/>
-    </row>
-    <row r="17" spans="3:11" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="10"/>
+    </row>
+    <row r="17" spans="3:17" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C17" s="10"/>
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
       <c r="F17" s="11"/>
       <c r="G17" s="10"/>
       <c r="H17" s="11"/>
-      <c r="I17" s="10"/>
+      <c r="I17" s="11"/>
       <c r="J17" s="11"/>
-      <c r="K17" s="10"/>
-    </row>
-    <row r="18" spans="3:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="10"/>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="10"/>
+    </row>
+    <row r="18" spans="3:17" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C18" s="10"/>
       <c r="D18" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E18" s="10"/>
-      <c r="F18" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I18" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="K18" s="10"/>
-    </row>
-    <row r="19" spans="3:11" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F18" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="9"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="10"/>
+    </row>
+    <row r="19" spans="3:17" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
       <c r="F19" s="11"/>
       <c r="G19" s="10"/>
       <c r="H19" s="11"/>
-      <c r="I19" s="10"/>
+      <c r="I19" s="11"/>
       <c r="J19" s="11"/>
-      <c r="K19" s="10"/>
-    </row>
-    <row r="20" spans="3:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="10"/>
+      <c r="P19" s="11"/>
+      <c r="Q19" s="10"/>
+    </row>
+    <row r="20" spans="3:17" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C20" s="10"/>
       <c r="D20" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E20" s="10"/>
-      <c r="F20" s="7" t="s">
-        <v>14</v>
+      <c r="F20" s="8" t="s">
+        <v>15</v>
       </c>
       <c r="G20" s="9"/>
       <c r="H20" s="2"/>
-      <c r="I20" s="9"/>
+      <c r="I20" s="2"/>
       <c r="J20" s="2"/>
-      <c r="K20" s="10"/>
-    </row>
-    <row r="21" spans="3:11" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="10"/>
+    </row>
+    <row r="21" spans="3:17" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="10"/>
       <c r="D21" s="10"/>
       <c r="E21" s="10"/>
       <c r="F21" s="11"/>
       <c r="G21" s="10"/>
       <c r="H21" s="11"/>
-      <c r="I21" s="10"/>
+      <c r="I21" s="11"/>
       <c r="J21" s="11"/>
-      <c r="K21" s="10"/>
-    </row>
-    <row r="22" spans="3:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="10"/>
+      <c r="P21" s="11"/>
+      <c r="Q21" s="10"/>
+    </row>
+    <row r="22" spans="3:17" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="10"/>
       <c r="D22" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E22" s="10"/>
       <c r="F22" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" s="9"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="9"/>
+        <v>16</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" s="2"/>
       <c r="J22" s="2"/>
-      <c r="K22" s="10"/>
-    </row>
-    <row r="23" spans="3:11" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="10"/>
+    </row>
+    <row r="23" spans="3:17" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C23" s="10"/>
       <c r="D23" s="10"/>
       <c r="E23" s="10"/>
-      <c r="F23" s="11"/>
+      <c r="F23" s="10"/>
       <c r="G23" s="10"/>
-      <c r="H23" s="11"/>
+      <c r="H23" s="10"/>
       <c r="I23" s="10"/>
-      <c r="J23" s="11"/>
+      <c r="J23" s="10"/>
       <c r="K23" s="10"/>
-    </row>
-    <row r="24" spans="3:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C24" s="10"/>
-      <c r="D24" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E24" s="10"/>
-      <c r="F24" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G24" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I24" s="9"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="10"/>
-    </row>
-    <row r="25" spans="3:11" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="10"/>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="D4:J4"/>
+    <mergeCell ref="D4:P4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
